--- a/01_data/raw_data/Burraco_et_al_estivation_hibernation.xlsx
+++ b/01_data/raw_data/Burraco_et_al_estivation_hibernation.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablocapillalasheras/Library/CloudStorage/Dropbox/PabloCL/2-Work drive/3-Active_projects/8 - Collaborations/01_Meta-analysis_hibernation/meta_analysis_hibernation/01_data/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34864E7F-9399-CA4E-AC80-F2F85EBFB851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B097A2-061D-0547-88D5-E0E30DF5DA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$T$518</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$T$473</definedName>
   </definedNames>
   <calcPr calcId="150001"/>
   <extLst>
@@ -24443,11 +24443,7 @@
       <c r="T473" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T518" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T518">
-      <sortCondition ref="A1:A518"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:T473" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T518">
     <sortCondition ref="C2:C518"/>
     <sortCondition ref="B2:B518"/>
